--- a/Employee_Reports_wi48/Lemuel Celeste Anacleto Q0150.xlsx
+++ b/Employee_Reports_wi48/Lemuel Celeste Anacleto Q0150.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -726,11 +726,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -775,11 +775,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -824,11 +824,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-113</v>
+        <v>-116</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -873,11 +873,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-114</v>
+        <v>-117</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -896,9 +896,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>05-Apr-2025</t>
@@ -910,11 +922,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-99</v>
+        <v>-102</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -959,11 +971,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1008,11 +1020,11 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1057,11 +1069,11 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1106,11 +1118,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1143,11 +1155,11 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1192,11 +1204,11 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1241,11 +1253,11 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1278,11 +1290,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1315,11 +1327,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1364,11 +1376,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1413,11 +1425,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1462,11 +1474,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1499,11 +1511,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1536,11 +1548,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1573,11 +1585,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
